--- a/Data/testData.xlsx
+++ b/Data/testData.xlsx
@@ -262,10 +262,10 @@
     <t>Slovakia</t>
   </si>
   <si>
-    <t>Cleve</t>
-  </si>
-  <si>
-    <t>Fay</t>
+    <t>Dandre</t>
+  </si>
+  <si>
+    <t>Bins-Hauck</t>
   </si>
   <si>
     <t>041/562 66 84</t>

--- a/Data/testData.xlsx
+++ b/Data/testData.xlsx
@@ -262,10 +262,10 @@
     <t>Slovakia</t>
   </si>
   <si>
-    <t>Dandre</t>
-  </si>
-  <si>
-    <t>Bins-Hauck</t>
+    <t>Blake</t>
+  </si>
+  <si>
+    <t>O'Keefe</t>
   </si>
   <si>
     <t>041/562 66 84</t>

--- a/Data/testData.xlsx
+++ b/Data/testData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="142">
   <si>
     <t xml:space="preserve">Serial </t>
   </si>
@@ -262,10 +262,10 @@
     <t>Slovakia</t>
   </si>
   <si>
-    <t>Blake</t>
-  </si>
-  <si>
-    <t>O'Keefe</t>
+    <t>Lonie</t>
+  </si>
+  <si>
+    <t>Ritchie</t>
   </si>
   <si>
     <t>041/562 66 84</t>
@@ -415,34 +415,31 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>Isabell</t>
-  </si>
-  <si>
-    <t>Beahan</t>
+    <t>Laurine</t>
+  </si>
+  <si>
+    <t>Test3</t>
+  </si>
+  <si>
+    <t>Destin</t>
+  </si>
+  <si>
+    <t>Nader</t>
+  </si>
+  <si>
+    <t>{"name":"Error"}</t>
+  </si>
+  <si>
+    <t>Test4</t>
+  </si>
+  <si>
+    <t>Eldridge</t>
+  </si>
+  <si>
+    <t>Cremin</t>
   </si>
   <si>
     <t>{}</t>
-  </si>
-  <si>
-    <t>Test3</t>
-  </si>
-  <si>
-    <t>Destin</t>
-  </si>
-  <si>
-    <t>Nader</t>
-  </si>
-  <si>
-    <t>{"name":"Error"}</t>
-  </si>
-  <si>
-    <t>Test4</t>
-  </si>
-  <si>
-    <t>Eldridge</t>
-  </si>
-  <si>
-    <t>Cremin</t>
   </si>
 </sst>
 </file>
@@ -1357,7 +1354,7 @@
         <v>133</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>84</v>
@@ -1582,7 +1579,7 @@
         <v>129</v>
       </c>
       <c r="CE3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="CF3" s="15" t="s">
         <v>131</v>
@@ -1590,7 +1587,7 @@
     </row>
     <row r="4" ht="14.4" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>80</v>
@@ -1599,10 +1596,10 @@
         <v>81</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>84</v>
@@ -1827,7 +1824,7 @@
         <v>129</v>
       </c>
       <c r="CE4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="CF4" s="15" t="s">
         <v>131</v>
@@ -1835,7 +1832,7 @@
     </row>
     <row r="5" ht="14.4" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>80</v>
@@ -1844,10 +1841,10 @@
         <v>81</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>84</v>
@@ -2072,7 +2069,7 @@
         <v>129</v>
       </c>
       <c r="CE5" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="CF5" s="15" t="s">
         <v>131</v>

--- a/Data/testData.xlsx
+++ b/Data/testData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="143">
   <si>
     <t xml:space="preserve">Serial </t>
   </si>
@@ -262,162 +262,168 @@
     <t>Slovakia</t>
   </si>
   <si>
-    <t>Lonie</t>
+    <t>Brett</t>
+  </si>
+  <si>
+    <t>Haag</t>
+  </si>
+  <si>
+    <t>041/562 66 84</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vysoká </t>
+  </si>
+  <si>
+    <t>Holíč</t>
+  </si>
+  <si>
+    <t>Street Address</t>
+  </si>
+  <si>
+    <t>department@retailassistant.com</t>
+  </si>
+  <si>
+    <t>01/07/2024</t>
+  </si>
+  <si>
+    <t>New Hire</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Agreement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retail Assistant Stockroom_NEW  </t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>38.75</t>
+  </si>
+  <si>
+    <t>2 - 2 (Slovakia Degree of Labour Difficulty-Slovakia)@5223001</t>
+  </si>
+  <si>
+    <t>5 Days</t>
+  </si>
+  <si>
+    <t>31/12/2024</t>
+  </si>
+  <si>
+    <t>Automation Comments here….</t>
+  </si>
+  <si>
+    <t>94 Retail Operatives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 Household  </t>
+  </si>
+  <si>
+    <t>Please select a Slovakia Pay Group</t>
+  </si>
+  <si>
+    <t>SK Monthly</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Všeobecná zdrav. Poisť. </t>
+  </si>
+  <si>
+    <t>Agreement on Student Work (DBPS)</t>
+  </si>
+  <si>
+    <t>Defaulted</t>
+  </si>
+  <si>
+    <t>Definite</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Personal ID Number (RC)</t>
+  </si>
+  <si>
+    <t>01/01/2000</t>
+  </si>
+  <si>
+    <t>01/01/2040</t>
+  </si>
+  <si>
+    <t>Romania</t>
+  </si>
+  <si>
+    <t>Identity Card Number</t>
+  </si>
+  <si>
+    <t>999943</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>16/08/2008</t>
+  </si>
+  <si>
+    <t>Bratislava</t>
+  </si>
+  <si>
+    <t>Single (Slovakia)</t>
+  </si>
+  <si>
+    <t>Citizen (Slovakia)</t>
+  </si>
+  <si>
+    <t>Nation Bank of Slovakia</t>
+  </si>
+  <si>
+    <t>KODBSKBXXXX</t>
+  </si>
+  <si>
+    <t>Checking</t>
+  </si>
+  <si>
+    <t>SK8975000000000012345671</t>
+  </si>
+  <si>
+    <t>Vseobecna zdrav. Poist</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Test2</t>
+  </si>
+  <si>
+    <t>Laurine</t>
   </si>
   <si>
     <t>Ritchie</t>
   </si>
   <si>
-    <t>041/562 66 84</t>
-  </si>
-  <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vysoká </t>
-  </si>
-  <si>
-    <t>Holíč</t>
-  </si>
-  <si>
-    <t>Street Address</t>
-  </si>
-  <si>
-    <t>department@retailassistant.com</t>
-  </si>
-  <si>
-    <t>01/07/2024</t>
-  </si>
-  <si>
-    <t>New Hire</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Agreement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retail Assistant Stockroom_NEW  </t>
-  </si>
-  <si>
-    <t>Full Time</t>
-  </si>
-  <si>
-    <t>38.75</t>
-  </si>
-  <si>
-    <t>2 - 2 (Slovakia Degree of Labour Difficulty-Slovakia)@5223001</t>
-  </si>
-  <si>
-    <t>5 Days</t>
-  </si>
-  <si>
-    <t>31/12/2024</t>
-  </si>
-  <si>
-    <t>Automation Comments here….</t>
-  </si>
-  <si>
-    <t>94 Retail Operatives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 Household  </t>
-  </si>
-  <si>
-    <t>Please select a Slovakia Pay Group</t>
-  </si>
-  <si>
-    <t>SK Monthly</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Všeobecná zdrav. Poisť. </t>
-  </si>
-  <si>
-    <t>Agreement on Student Work (DBPS)</t>
-  </si>
-  <si>
-    <t>Defaulted</t>
-  </si>
-  <si>
-    <t>Definite</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Personal ID Number (RC)</t>
-  </si>
-  <si>
-    <t>01/01/2000</t>
-  </si>
-  <si>
-    <t>01/01/2040</t>
-  </si>
-  <si>
-    <t>Romania</t>
-  </si>
-  <si>
-    <t>Identity Card Number</t>
-  </si>
-  <si>
-    <t>999943</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>16/08/2008</t>
-  </si>
-  <si>
-    <t>Bratislava</t>
-  </si>
-  <si>
-    <t>Single (Slovakia)</t>
-  </si>
-  <si>
-    <t>Citizen (Slovakia)</t>
-  </si>
-  <si>
-    <t>Nation Bank of Slovakia</t>
-  </si>
-  <si>
-    <t>KODBSKBXXXX</t>
-  </si>
-  <si>
-    <t>Checking</t>
-  </si>
-  <si>
-    <t>SK8975000000000012345671</t>
-  </si>
-  <si>
-    <t>Vseobecna zdrav. Poist</t>
-  </si>
-  <si>
     <t>{"name":"TimeoutError"}</t>
   </si>
   <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>Test2</t>
-  </si>
-  <si>
-    <t>Laurine</t>
-  </si>
-  <si>
     <t>Test3</t>
   </si>
   <si>
@@ -437,9 +443,6 @@
   </si>
   <si>
     <t>Cremin</t>
-  </si>
-  <si>
-    <t>{}</t>
   </si>
 </sst>
 </file>
@@ -1354,7 +1357,7 @@
         <v>133</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>84</v>
@@ -1579,7 +1582,7 @@
         <v>129</v>
       </c>
       <c r="CE3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="CF3" s="15" t="s">
         <v>131</v>
@@ -1587,7 +1590,7 @@
     </row>
     <row r="4" ht="14.4" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>80</v>
@@ -1596,10 +1599,10 @@
         <v>81</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>84</v>
@@ -1824,7 +1827,7 @@
         <v>129</v>
       </c>
       <c r="CE4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="CF4" s="15" t="s">
         <v>131</v>
@@ -1832,7 +1835,7 @@
     </row>
     <row r="5" ht="14.4" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>80</v>
@@ -1841,10 +1844,10 @@
         <v>81</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>84</v>
@@ -2069,7 +2072,7 @@
         <v>129</v>
       </c>
       <c r="CE5" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="CF5" s="15" t="s">
         <v>131</v>
